--- a/tasks/medical_careig_specialty_pharmacy_d3e312a5/environment/initial_workspace/intake_blank.xlsx
+++ b/tasks/medical_careig_specialty_pharmacy_d3e312a5/environment/initial_workspace/intake_blank.xlsx
@@ -3,6 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15"/>
+  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC226E9D-A5EE-413E-9E80-3DAACE470FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3036" yWindow="744" windowWidth="13860" windowHeight="11064" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
